--- a/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y vacunación</t>
+          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-24,92</t>
+          <t>22,31</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-43,21</t>
+          <t>12,53</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-33,32</t>
+          <t>17,77</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 22,51</t>
+          <t>-0,93; 22,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 14,14</t>
+          <t>-9,51; 14,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 2,17</t>
+          <t>4,86; 35,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 16,28</t>
+          <t>-6,72; 16,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 11,89</t>
+          <t>-9,44; 12,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-59,53; -23,22</t>
+          <t>-7,81; 31,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 16,57</t>
+          <t>-0,04; 16,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 10,94</t>
+          <t>-6,29; 11,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-45,65; -14,96</t>
+          <t>5,38; 29,47</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-42,73%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-68,66%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-55,06%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,08; 44,4</t>
+          <t>-1,05; 41,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,83; 26,89</t>
+          <t>-14,63; 26,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,39; 6,01</t>
+          <t>7,75; 66,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 29,25</t>
+          <t>-10,06; 28,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 21,35</t>
+          <t>-13,68; 20,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,67; -37,65</t>
+          <t>-10,28; 56,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 30,04</t>
+          <t>0,06; 29,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 19,52</t>
+          <t>-9,56; 19,62</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-74,3; -24,37</t>
+          <t>8,38; 52,1</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-15,84</t>
+          <t>20,84</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-23,21</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-20,22</t>
+          <t>23,52</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 18,01</t>
+          <t>-5,91; 17,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 15,08</t>
+          <t>-9,84; 14,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-40,2; 10,64</t>
+          <t>-6,08; 37,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 11,98</t>
+          <t>-14,51; 9,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 12,08</t>
+          <t>-12,5; 11,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-44,29; 0,2</t>
+          <t>5,67; 39,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 10,92</t>
+          <t>-6,54; 11,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 10,61</t>
+          <t>-7,29; 10,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,01; -0,77</t>
+          <t>6,41; 34,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-26,59%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-38,47%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-33,73%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 34,77</t>
+          <t>-8,94; 34,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 28,76</t>
+          <t>-15,02; 27,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 18,29</t>
+          <t>-5,69; 71,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,25; 23,41</t>
+          <t>-22,12; 18,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 22,48</t>
+          <t>-19,0; 21,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,91; 0,49</t>
+          <t>9,86; 72,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 19,79</t>
+          <t>-10,49; 21,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 18,96</t>
+          <t>-11,01; 18,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -1,48</t>
+          <t>10,48; 61,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-71,21</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-36,16</t>
+          <t>-11,37</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-44,39</t>
+          <t>-7,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 11,95</t>
+          <t>-13,0; 11,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 9,27</t>
+          <t>-18,88; 9,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-79,67; -60,9</t>
+          <t>-41,61; 32,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 13,91</t>
+          <t>-10,02; 12,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 0,88</t>
+          <t>-24,85; 0,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-60,82; -9,54</t>
+          <t>-38,89; 11,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 8,3</t>
+          <t>-8,58; 8,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 0,51</t>
+          <t>-17,53; 0,94</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-63,68; -20,6</t>
+          <t>-32,0; 11,06</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-50,31%</t>
+          <t>-15,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-61,99%</t>
+          <t>-9,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,64; 18,85</t>
+          <t>-15,98; 18,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 14,65</t>
+          <t>-24,47; 15,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-57,39; 49,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 21,02</t>
+          <t>-12,95; 18,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 1,52</t>
+          <t>-33,13; 0,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,97; -12,1</t>
+          <t>-52,82; 16,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 12,27</t>
+          <t>-11,31; 12,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,32; 0,79</t>
+          <t>-23,26; 1,45</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-88,15; -29,81</t>
+          <t>-44,88; 15,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-19,63</t>
+          <t>11,77</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-36,92</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-29,42</t>
+          <t>14,94</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 4,79</t>
+          <t>-10,46; 5,31</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 13,65</t>
+          <t>-2,71; 12,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-35,4; -4,46</t>
+          <t>-4,34; 24,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 6,77</t>
+          <t>-8,65; 7,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 10,68</t>
+          <t>-5,45; 10,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-49,57; -21,84</t>
+          <t>3,54; 26,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 4,18</t>
+          <t>-6,84; 4,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 9,85</t>
+          <t>-1,19; 10,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-38,84; -18,26</t>
+          <t>5,78; 23,52</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-31,89%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-57,58%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,8%</t>
+          <t>23,77%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,3; 8,4</t>
+          <t>-16,15; 9,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 23,78</t>
+          <t>-4,13; 22,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-55,77; -7,22</t>
+          <t>-6,25; 42,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 11,24</t>
+          <t>-12,98; 11,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 18,07</t>
+          <t>-7,94; 17,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-75,24; -34,76</t>
+          <t>5,6; 44,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 6,86</t>
+          <t>-10,44; 7,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 16,22</t>
+          <t>-1,75; 17,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-61,57; -29,79</t>
+          <t>9,14; 39,13</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-20,12</t>
+          <t>22,0</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-17,55</t>
+          <t>19,45</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-18,3</t>
+          <t>20,78</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 21,29</t>
+          <t>-0,92; 20,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 21,4</t>
+          <t>-0,29; 21,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 1,83</t>
+          <t>1,97; 35,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 12,47</t>
+          <t>-8,83; 10,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 16,48</t>
+          <t>-4,49; 16,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-35,35; 1,89</t>
+          <t>6,94; 30,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 13,02</t>
+          <t>-1,91; 12,63</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 15,52</t>
+          <t>0,41; 15,16</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-31,62; -4,77</t>
+          <t>9,66; 29,73</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-33,96%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-26,88%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-29,26%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 40,37</t>
+          <t>-1,22; 39,18</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 40,86</t>
+          <t>-0,45; 40,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-61,86; 3,09</t>
+          <t>3,7; 67,26</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 21,52</t>
+          <t>-12,27; 18,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 27,46</t>
+          <t>-6,32; 26,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,41; 2,53</t>
+          <t>10,83; 50,57</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 22,53</t>
+          <t>-2,82; 21,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,53; 27,0</t>
+          <t>0,63; 26,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-48,72; -7,94</t>
+          <t>15,28; 51,6</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-33,8</t>
+          <t>7,73</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-42,32</t>
+          <t>14,85</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-38,98</t>
+          <t>11,23</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 2,87</t>
+          <t>-26,5; 4,12</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-32,66; -5,01</t>
+          <t>-31,58; -2,98</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-58,35; -4,05</t>
+          <t>-23,45; 24,57</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-16,46; 10,87</t>
+          <t>-18,44; 9,56</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 8,53</t>
+          <t>-17,26; 9,74</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-61,01; -15,27</t>
+          <t>-15,27; 33,47</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-15,93; 2,23</t>
+          <t>-16,6; 2,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,18; -2,62</t>
+          <t>-21,28; -1,41</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-55,36; -19,66</t>
+          <t>-8,67; 24,65</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-46,53%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-64,53%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-56,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,29; 4,07</t>
+          <t>-33,87; 5,89</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,25; -7,57</t>
+          <t>-42,24; -4,76</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-79,57; -6,17</t>
+          <t>-31,25; 35,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 18,45</t>
+          <t>-25,97; 15,63</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 14,3</t>
+          <t>-24,58; 16,02</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-89,61; -22,93</t>
+          <t>-20,52; 55,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 3,47</t>
+          <t>-22,19; 4,19</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,22; -3,59</t>
+          <t>-29,08; -2,07</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-78,21; -28,41</t>
+          <t>-11,88; 37,35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-25,11</t>
+          <t>15,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-32,62</t>
+          <t>14,84</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-29,26</t>
+          <t>15,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 7,02</t>
+          <t>-2,2; 7,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,06</t>
+          <t>-2,89; 6,55</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-33,72; -15,61</t>
+          <t>7,05; 22,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 4,41</t>
+          <t>-4,19; 4,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,84</t>
+          <t>-4,56; 4,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-39,88; -24,03</t>
+          <t>7,38; 21,27</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 4,79</t>
+          <t>-1,93; 4,35</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,14</t>
+          <t>-2,06; 4,73</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-34,89; -23,07</t>
+          <t>10,23; 20,27</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-40,01%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-50,23%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-45,81%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 11,77</t>
+          <t>-3,36; 11,8</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 10,04</t>
+          <t>-4,54; 10,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-52,42; -25,79</t>
+          <t>11,21; 37,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,1</t>
+          <t>-6,17; 6,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 7,81</t>
+          <t>-6,82; 7,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-60,63; -37,76</t>
+          <t>11,23; 33,44</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 7,78</t>
+          <t>-2,91; 6,9</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 6,6</t>
+          <t>-3,07; 7,73</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-54,12; -36,58</t>
+          <t>15,48; 32,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 22,01</t>
+          <t>-0,43; 22,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 14,45</t>
+          <t>-9,89; 14,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 35,23</t>
+          <t>4,88; 36,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 16,19</t>
+          <t>-6,59; 16,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,44; 12,13</t>
+          <t>-10,1; 12,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 31,91</t>
+          <t>-9,01; 28,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 16,5</t>
+          <t>-0,4; 15,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 11,02</t>
+          <t>-6,66; 10,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,38; 29,47</t>
+          <t>3,31; 29,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 41,71</t>
+          <t>-0,72; 44,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 26,9</t>
+          <t>-15,5; 27,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,75; 66,41</t>
+          <t>8,71; 70,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 28,0</t>
+          <t>-9,65; 28,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 20,93</t>
+          <t>-15,26; 21,77</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 56,57</t>
+          <t>-13,82; 48,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 29,4</t>
+          <t>-0,59; 29,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 19,62</t>
+          <t>-10,18; 19,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,38; 52,1</t>
+          <t>4,71; 51,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 17,99</t>
+          <t>-7,68; 16,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,84; 14,43</t>
+          <t>-10,49; 13,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,08; 37,93</t>
+          <t>-9,49; 36,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,51; 9,7</t>
+          <t>-13,72; 11,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 11,43</t>
+          <t>-11,99; 12,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 39,06</t>
+          <t>6,35; 38,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 11,52</t>
+          <t>-7,69; 10,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 10,17</t>
+          <t>-8,22; 9,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 34,67</t>
+          <t>8,86; 34,8</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 34,72</t>
+          <t>-11,65; 31,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 27,77</t>
+          <t>-16,1; 25,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 71,03</t>
+          <t>-14,62; 67,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 18,07</t>
+          <t>-20,34; 20,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-19,0; 21,47</t>
+          <t>-18,28; 24,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 72,56</t>
+          <t>10,69; 72,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 21,43</t>
+          <t>-11,79; 20,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 18,59</t>
+          <t>-12,51; 17,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,48; 61,28</t>
+          <t>15,0; 61,64</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,0; 11,75</t>
+          <t>-12,34; 12,85</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 9,62</t>
+          <t>-18,38; 9,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-41,61; 32,92</t>
+          <t>-42,05; 33,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 12,51</t>
+          <t>-9,14; 13,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 0,69</t>
+          <t>-24,86; 1,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,89; 11,24</t>
+          <t>-38,36; 12,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 8,46</t>
+          <t>-6,73; 10,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-17,53; 0,94</t>
+          <t>-18,66; 0,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-32,0; 11,06</t>
+          <t>-31,07; 12,99</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 18,85</t>
+          <t>-16,13; 20,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,47; 15,01</t>
+          <t>-24,41; 14,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 49,1</t>
+          <t>-56,61; 49,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 18,6</t>
+          <t>-12,16; 21,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 0,83</t>
+          <t>-32,14; 2,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 16,74</t>
+          <t>-53,7; 18,48</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 12,35</t>
+          <t>-9,03; 15,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 1,45</t>
+          <t>-24,58; 0,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 15,98</t>
+          <t>-42,61; 18,73</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 5,31</t>
+          <t>-10,85; 5,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 12,8</t>
+          <t>-2,65; 13,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 24,91</t>
+          <t>-3,3; 25,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,65; 7,01</t>
+          <t>-8,77; 6,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 10,45</t>
+          <t>-5,26; 10,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 26,95</t>
+          <t>3,22; 26,73</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,61</t>
+          <t>-7,13; 3,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 10,05</t>
+          <t>-1,79; 9,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 23,52</t>
+          <t>4,69; 23,68</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 9,4</t>
+          <t>-16,89; 9,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 22,36</t>
+          <t>-4,18; 22,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 42,65</t>
+          <t>-5,19; 43,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-12,98; 11,79</t>
+          <t>-13,06; 11,76</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 17,72</t>
+          <t>-7,94; 16,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,6; 44,13</t>
+          <t>5,06; 43,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 7,72</t>
+          <t>-10,87; 6,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 17,05</t>
+          <t>-2,63; 16,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,14; 39,13</t>
+          <t>8,01; 39,22</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 20,37</t>
+          <t>-0,41; 20,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 21,47</t>
+          <t>-1,14; 20,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 35,91</t>
+          <t>3,52; 36,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 10,75</t>
+          <t>-7,79; 12,94</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 16,0</t>
+          <t>-3,17; 16,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,94; 30,33</t>
+          <t>5,08; 30,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 12,63</t>
+          <t>-1,49; 13,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 15,16</t>
+          <t>0,01; 14,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,66; 29,73</t>
+          <t>9,65; 29,6</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 39,18</t>
+          <t>-0,27; 38,7</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 40,98</t>
+          <t>-1,7; 40,4</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3,7; 67,26</t>
+          <t>5,43; 67,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 18,2</t>
+          <t>-10,75; 22,06</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 26,69</t>
+          <t>-4,28; 28,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,83; 50,57</t>
+          <t>7,78; 51,63</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 21,48</t>
+          <t>-2,06; 23,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,63; 26,0</t>
+          <t>0,05; 25,35</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>15,28; 51,6</t>
+          <t>14,41; 50,28</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-26,5; 4,12</t>
+          <t>-25,53; 3,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-31,58; -2,98</t>
+          <t>-31,61; -2,76</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 24,57</t>
+          <t>-19,1; 25,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 9,56</t>
+          <t>-17,69; 10,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,26; 9,74</t>
+          <t>-17,64; 10,55</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 33,47</t>
+          <t>-16,01; 33,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-16,6; 2,79</t>
+          <t>-17,2; 2,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,28; -1,41</t>
+          <t>-20,56; -1,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-8,67; 24,65</t>
+          <t>-9,72; 23,93</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,87; 5,89</t>
+          <t>-33,22; 5,16</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-42,24; -4,76</t>
+          <t>-40,9; -4,28</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,25; 35,16</t>
+          <t>-24,83; 38,28</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 15,63</t>
+          <t>-24,82; 17,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 16,02</t>
+          <t>-24,85; 17,41</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 55,62</t>
+          <t>-20,84; 56,82</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-22,19; 4,19</t>
+          <t>-23,19; 4,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-29,08; -2,07</t>
+          <t>-28,49; -2,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 37,35</t>
+          <t>-13,36; 36,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 7,04</t>
+          <t>-2,25; 6,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 6,55</t>
+          <t>-2,82; 6,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,05; 22,96</t>
+          <t>6,86; 22,47</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 4,38</t>
+          <t>-3,89; 4,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 4,67</t>
+          <t>-3,87; 4,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,38; 21,27</t>
+          <t>6,85; 20,87</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,35</t>
+          <t>-2,04; 4,05</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,73</t>
+          <t>-2,26; 4,11</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>10,23; 20,27</t>
+          <t>9,27; 19,96</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 11,8</t>
+          <t>-3,43; 11,02</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 10,81</t>
+          <t>-4,35; 10,52</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11,21; 37,66</t>
+          <t>10,82; 36,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 6,95</t>
+          <t>-5,81; 7,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 7,43</t>
+          <t>-5,82; 7,62</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,23; 33,44</t>
+          <t>10,59; 32,93</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,9</t>
+          <t>-3,1; 6,49</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,73</t>
+          <t>-3,47; 6,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,48; 32,6</t>
+          <t>13,97; 31,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP18A03-Clase-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por diagnóstico y tratamiento</t>
+          <t>Menores cuya última consulta médica fue por diagnóstico y tratamiento</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10,85</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,18</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22,31</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,74</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,53</t>
+          <t>19,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17,77</t>
+          <t>15,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 22,52</t>
+          <t>-6,06; 16,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 14,79</t>
+          <t>-12,03; 11,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 36,73</t>
+          <t>-11,8; 28,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 16,81</t>
+          <t>-0,09; 22,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,1; 12,25</t>
+          <t>-10,39; 14,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,01; 28,19</t>
+          <t>-0,97; 34,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 15,99</t>
+          <t>-0,71; 16,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 10,71</t>
+          <t>-6,83; 10,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,78</t>
+          <t>1,38; 28,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,51%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,24%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>19,17%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,24%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>38,26%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 44,06</t>
+          <t>-8,98; 29,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 27,84</t>
+          <t>-17,25; 21,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,71; 70,04</t>
+          <t>-18,25; 50,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 28,91</t>
+          <t>0,08; 44,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-15,26; 21,77</t>
+          <t>-15,83; 26,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,82; 48,03</t>
+          <t>-1,15; 65,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 29,62</t>
+          <t>-0,97; 30,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 19,03</t>
+          <t>-10,66; 19,52</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 51,44</t>
+          <t>2,18; 49,64</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24,36</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>5,96</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2,57</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>20,84</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,1</t>
+          <t>20,31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23,52</t>
+          <t>22,86</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 16,94</t>
+          <t>-12,92; 11,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 13,63</t>
+          <t>-12,06; 12,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 36,78</t>
+          <t>5,09; 38,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 11,19</t>
+          <t>-5,9; 18,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 12,83</t>
+          <t>-8,9; 15,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 38,55</t>
+          <t>-6,74; 39,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 10,91</t>
+          <t>-6,46; 10,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 9,97</t>
+          <t>-7,12; 10,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 34,8</t>
+          <t>8,18; 35,47</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-2,42%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-0,02%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>9,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,42%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-0,02%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,65; 31,4</t>
+          <t>-19,25; 23,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 25,9</t>
+          <t>-18,08; 22,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 67,12</t>
+          <t>8,41; 71,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 20,98</t>
+          <t>-8,75; 34,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 24,42</t>
+          <t>-13,73; 28,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 72,27</t>
+          <t>-10,0; 72,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 20,32</t>
+          <t>-10,79; 19,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 17,91</t>
+          <t>-11,19; 18,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,0; 61,64</t>
+          <t>14,53; 65,01</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-11,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-12,15</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,67</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,15</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>6,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-11,79</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-11,37</t>
+          <t>5,78</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,01</t>
+          <t>-7,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,34; 12,85</t>
+          <t>-9,07; 13,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-18,38; 9,38</t>
+          <t>-23,69; 0,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 33,22</t>
+          <t>-41,4; 10,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 13,44</t>
+          <t>-12,73; 11,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,86; 1,44</t>
+          <t>-18,18; 9,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-38,36; 12,97</t>
+          <t>-49,94; 33,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 10,06</t>
+          <t>-8,17; 8,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 0,4</t>
+          <t>-18,42; 0,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 12,99</t>
+          <t>-33,24; 12,32</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-16,4%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-16,9%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-0,94%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-7,23%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-16,4%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-15,82%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-9,79%</t>
+          <t>-10,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 20,59</t>
+          <t>-11,95; 21,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 14,96</t>
+          <t>-31,29; 1,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-56,61; 49,81</t>
+          <t>-56,62; 15,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 21,06</t>
+          <t>-16,64; 18,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 2,06</t>
+          <t>-23,2; 14,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,7; 18,48</t>
+          <t>-68,68; 49,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 15,05</t>
+          <t>-10,93; 12,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,58; 0,53</t>
+          <t>-24,32; 0,79</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 18,73</t>
+          <t>-45,13; 17,98</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,97</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>17,03</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-2,44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,97</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11,77</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,97</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,8</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,96</t>
+          <t>9,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,94</t>
+          <t>13,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 5,79</t>
+          <t>-8,42; 6,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 13,12</t>
+          <t>-5,06; 10,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 25,86</t>
+          <t>3,65; 27,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 6,83</t>
+          <t>-9,99; 4,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 10,3</t>
+          <t>-2,47; 13,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 26,73</t>
+          <t>-6,6; 22,94</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 3,89</t>
+          <t>-6,87; 4,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 9,51</t>
+          <t>-1,74; 9,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,69; 23,68</t>
+          <t>2,83; 22,42</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-1,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>26,56%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-3,97%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>8,07%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,52%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 9,99</t>
+          <t>-12,4; 11,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 22,87</t>
+          <t>-7,45; 18,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 43,79</t>
+          <t>5,87; 46,06</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 11,76</t>
+          <t>-15,3; 8,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 16,98</t>
+          <t>-3,83; 23,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,06; 43,98</t>
+          <t>-10,29; 38,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 6,44</t>
+          <t>-10,55; 6,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 16,07</t>
+          <t>-2,61; 16,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8,01; 39,22</t>
+          <t>4,31; 36,69</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6,32</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>19,79</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>10,07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>10,11</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>22,0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,32</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,45</t>
+          <t>21,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,78</t>
+          <t>20,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 20,05</t>
+          <t>-7,56; 12,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 20,72</t>
+          <t>-4,19; 16,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,52; 36,4</t>
+          <t>5,19; 31,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,79; 12,94</t>
+          <t>-1,03; 21,29</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 16,33</t>
+          <t>-0,87; 21,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,08; 30,49</t>
+          <t>0,63; 35,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 13,59</t>
+          <t>-1,98; 13,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,01; 14,91</t>
+          <t>0,36; 15,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,65; 29,6</t>
+          <t>9,57; 30,56</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>17,06%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>37,13%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9,68%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 38,7</t>
+          <t>-10,72; 21,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 40,4</t>
+          <t>-5,83; 27,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5,43; 67,83</t>
+          <t>7,83; 52,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 22,06</t>
+          <t>-1,74; 40,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 28,04</t>
+          <t>-1,39; 40,86</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,78; 51,63</t>
+          <t>3,02; 68,2</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 23,75</t>
+          <t>-3,03; 22,53</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>0,05; 25,35</t>
+          <t>0,53; 27,0</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>14,41; 50,28</t>
+          <t>15,14; 53,24</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-3,45</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-4,42</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>14,17</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-11,02</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-18,38</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>7,73</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-3,45</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,85</t>
+          <t>8,54</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11,23</t>
+          <t>11,26</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-25,53; 3,35</t>
+          <t>-16,46; 10,87</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-31,61; -2,76</t>
+          <t>-18,7; 8,53</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-19,1; 25,61</t>
+          <t>-14,33; 32,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-17,69; 10,08</t>
+          <t>-25,02; 2,87</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 10,55</t>
+          <t>-32,66; -5,01</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 33,59</t>
+          <t>-21,1; 26,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-17,2; 2,73</t>
+          <t>-15,93; 2,23</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -1,77</t>
+          <t>-21,18; -2,62</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 23,93</t>
+          <t>-6,23; 24,97</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-5,27%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-6,74%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>21,6%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-15,17%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-25,3%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>10,65%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-5,27%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-6,74%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-33,22; 5,16</t>
+          <t>-23,44; 18,45</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-40,9; -4,28</t>
+          <t>-26,03; 14,3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 38,28</t>
+          <t>-20,19; 55,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-24,82; 17,42</t>
+          <t>-33,29; 4,07</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-24,85; 17,41</t>
+          <t>-42,25; -7,57</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 56,82</t>
+          <t>-27,75; 39,41</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 4,16</t>
+          <t>-21,64; 3,47</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-28,49; -2,98</t>
+          <t>-29,22; -3,59</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-13,36; 36,1</t>
+          <t>-8,5; 37,8</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>0,25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>0,19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>14,53</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>2,48</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>1,78</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>15,6</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,19</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,84</t>
+          <t>14,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15,29</t>
+          <t>14,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,67</t>
+          <t>-3,93; 4,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 6,41</t>
+          <t>-3,8; 4,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,86; 22,47</t>
+          <t>7,76; 20,55</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,63</t>
+          <t>-2,32; 7,02</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 4,77</t>
+          <t>-3,05; 6,06</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,85; 20,87</t>
+          <t>4,84; 21,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 4,05</t>
+          <t>-1,45; 4,79</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,11</t>
+          <t>-1,95; 4,14</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,96</t>
+          <t>9,59; 19,62</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>22,37%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>3,96%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>2,83%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>24,86%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,61%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 11,02</t>
+          <t>-5,81; 7,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 10,52</t>
+          <t>-5,7; 7,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10,82; 36,78</t>
+          <t>11,76; 32,63</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,48</t>
+          <t>-3,51; 11,77</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 7,62</t>
+          <t>-4,56; 10,04</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10,59; 32,93</t>
+          <t>7,57; 34,86</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,49</t>
+          <t>-2,18; 7,78</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,52</t>
+          <t>-2,96; 6,6</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>13,97; 31,64</t>
+          <t>14,65; 31,09</t>
         </is>
       </c>
     </row>
